--- a/B_Thermal/B_results/single_annular_avg_analysis.xlsx
+++ b/B_Thermal/B_results/single_annular_avg_analysis.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>n_annuli</t>
+          <t>n_samples</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -495,19 +495,19 @@
         <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8370079282744509</v>
+        <v>16.59040485885801</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1734733418011373</v>
+        <v>0.2941781164637899</v>
       </c>
       <c r="F2" t="n">
-        <v>12.51746894714184</v>
+        <v>1038.805087840366</v>
       </c>
       <c r="G2" t="n">
-        <v>415.9594861211071</v>
+        <v>12003.65050354092</v>
       </c>
       <c r="H2" t="n">
         <v>5.034499813546447</v>
@@ -532,19 +532,19 @@
         <v>0.35</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3564104260437597</v>
+        <v>7.035671172860873</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04690628445021011</v>
+        <v>0.08691246062329167</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7664536951288048</v>
+        <v>74.05112585961588</v>
       </c>
       <c r="G3" t="n">
-        <v>348.3564503308843</v>
+        <v>9803.193489796937</v>
       </c>
       <c r="H3" t="n">
         <v>4.741757949432081</v>
@@ -569,19 +569,19 @@
         <v>0.5</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>1.447435544055829</v>
+        <v>17.82264741905594</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06158725734508145</v>
+        <v>0.3273743811180114</v>
       </c>
       <c r="F4" t="n">
-        <v>1.21273773131239</v>
+        <v>974.3153580549333</v>
       </c>
       <c r="G4" t="n">
-        <v>319.7313058699435</v>
+        <v>9090.968804657296</v>
       </c>
       <c r="H4" t="n">
         <v>4.341510236724118</v>
@@ -606,19 +606,19 @@
         <v>0.75</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6212481691636735</v>
+        <v>14.2027655977602</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0408005951024699</v>
+        <v>0.09873106456613162</v>
       </c>
       <c r="F5" t="n">
-        <v>4.243759947239778</v>
+        <v>698.3418394447772</v>
       </c>
       <c r="G5" t="n">
-        <v>2549.281617827229</v>
+        <v>71640.79933933764</v>
       </c>
       <c r="H5" t="n">
         <v>3.44262096412813</v>
@@ -643,19 +643,19 @@
         <v>1.1</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1520928450863644</v>
+        <v>11.68072660863329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01765418567929638</v>
+        <v>0.1398848038107719</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1797485800784834</v>
+        <v>313.997316478479</v>
       </c>
       <c r="G6" t="n">
-        <v>576.7267404926506</v>
+        <v>16046.66774128612</v>
       </c>
       <c r="H6" t="n">
         <v>2.487245077372206</v>
@@ -680,19 +680,19 @@
         <v>1.6</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.384531998621199</v>
+        <v>10.40881213393735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01745959601996335</v>
+        <v>0.2220724688909367</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05522110312231785</v>
+        <v>266.5074471166984</v>
       </c>
       <c r="G7" t="n">
-        <v>181.1493151521653</v>
+        <v>5404.056829595333</v>
       </c>
       <c r="H7" t="n">
         <v>2.665604702506965</v>
@@ -717,19 +717,19 @@
         <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4547171618120038</v>
+        <v>8.773803714745615</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01517373133181468</v>
+        <v>0.07520873238011791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1625546721718647</v>
+        <v>110.4397527874738</v>
       </c>
       <c r="G8" t="n">
-        <v>706.0162162578118</v>
+        <v>19524.90314262347</v>
       </c>
       <c r="H8" t="n">
         <v>2.069305622134722</v>
@@ -752,19 +752,19 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>119</v>
+        <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>4.25344407305728</v>
+        <v>86.51483150585126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06127465997250665</v>
+        <v>0.1556399173226612</v>
       </c>
       <c r="F9" t="n">
-        <v>19.13794467619548</v>
+        <v>3476.457927582344</v>
       </c>
       <c r="G9" t="n">
-        <v>5097.221132051792</v>
+        <v>143514.2398508377</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
